--- a/artfynd/A 3721-2023 artfynd.xlsx
+++ b/artfynd/A 3721-2023 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>136184749</v>
       </c>
       <c r="B6" t="n">
-        <v>58019</v>
+        <v>58021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
